--- a/planilhas/Copa do Brasil.xlsx
+++ b/planilhas/Copa do Brasil.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kleberson\Desktop\meu-site - Copia\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7980532-8F82-4921-9A84-A55188B1E9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2BE26B-C8ED-4987-9B8D-DC34DDE6C48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4F49A5ED-3A92-472E-8FA7-25B42F4FCE77}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4F49A5ED-3A92-472E-8FA7-25B42F4FCE77}"/>
   </bookViews>
   <sheets>
     <sheet name="Jogos" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="141">
   <si>
     <t>IDA</t>
   </si>
@@ -1168,7 +1168,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>53</xdr:col>
-      <xdr:colOff>602830</xdr:colOff>
+      <xdr:colOff>602831</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>231321</xdr:rowOff>
     </xdr:to>
@@ -1375,7 +1375,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>99</xdr:col>
-      <xdr:colOff>479425</xdr:colOff>
+      <xdr:colOff>479424</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>231321</xdr:rowOff>
     </xdr:to>
@@ -1480,7 +1480,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>88</xdr:col>
-      <xdr:colOff>54430</xdr:colOff>
+      <xdr:colOff>54429</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>17160</xdr:rowOff>
     </xdr:to>
@@ -1885,12 +1885,12 @@
     <col min="4" max="4" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="4.28515625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="30.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.28515625" style="3" customWidth="1"/>
     <col min="9" max="9" width="5.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="4.28515625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="26.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="5.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -1936,7 +1936,7 @@
     <col min="63" max="63" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="64" max="64" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="65" max="65" width="5.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="28.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="39.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="67" max="68" width="4.28515625" style="3" customWidth="1"/>
     <col min="69" max="69" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="70" max="70" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -2959,7 +2959,9 @@
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="L24" s="4"/>
-      <c r="N24" s="8"/>
+      <c r="N24" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="O24" s="9">
         <v>0</v>
       </c>
@@ -3039,7 +3041,9 @@
       <c r="BM24" s="10">
         <v>0</v>
       </c>
-      <c r="BN24" s="10"/>
+      <c r="BN24" s="10" t="s">
+        <v>16</v>
+      </c>
       <c r="BO24" s="32"/>
       <c r="BU24" s="4"/>
       <c r="CC24" s="3"/>
@@ -3070,7 +3074,9 @@
       <c r="E25" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N25" s="13"/>
+      <c r="N25" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="O25" s="14">
         <v>0</v>
       </c>
@@ -3150,7 +3156,9 @@
       <c r="BM25" s="15">
         <v>0</v>
       </c>
-      <c r="BN25" s="15"/>
+      <c r="BN25" s="15" t="s">
+        <v>69</v>
+      </c>
       <c r="BO25" s="32"/>
       <c r="BU25" s="4"/>
       <c r="BW25" s="4" t="s">
@@ -4379,7 +4387,9 @@
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="L40" s="4"/>
-      <c r="N40" s="8"/>
+      <c r="N40" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="O40" s="9">
         <v>0</v>
       </c>
@@ -4459,7 +4469,9 @@
       <c r="BM40" s="10">
         <v>0</v>
       </c>
-      <c r="BN40" s="10"/>
+      <c r="BN40" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="BO40" s="32"/>
       <c r="BU40" s="4"/>
       <c r="CC40" s="3"/>
@@ -4477,7 +4489,9 @@
       <c r="E41" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N41" s="13"/>
+      <c r="N41" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="O41" s="14">
         <v>0</v>
       </c>
@@ -4557,7 +4571,9 @@
       <c r="BM41" s="15">
         <v>0</v>
       </c>
-      <c r="BN41" s="15"/>
+      <c r="BN41" s="15" t="s">
+        <v>37</v>
+      </c>
       <c r="BO41" s="32"/>
       <c r="BU41" s="4"/>
       <c r="BW41" s="4" t="s">
@@ -5507,7 +5523,9 @@
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="L56" s="4"/>
-      <c r="N56" s="8"/>
+      <c r="N56" s="8" t="s">
+        <v>88</v>
+      </c>
       <c r="O56" s="9">
         <v>0</v>
       </c>
@@ -5554,7 +5572,9 @@
       <c r="BM56" s="10">
         <v>0</v>
       </c>
-      <c r="BN56" s="10"/>
+      <c r="BN56" s="10" t="s">
+        <v>99</v>
+      </c>
       <c r="BO56" s="32"/>
       <c r="BU56" s="4"/>
       <c r="CC56" s="3"/>
@@ -5572,7 +5592,9 @@
       <c r="E57" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N57" s="13"/>
+      <c r="N57" s="13" t="s">
+        <v>54</v>
+      </c>
       <c r="O57" s="14">
         <v>0</v>
       </c>
@@ -5629,7 +5651,9 @@
       <c r="BM57" s="15">
         <v>0</v>
       </c>
-      <c r="BN57" s="15"/>
+      <c r="BN57" s="15" t="s">
+        <v>124</v>
+      </c>
       <c r="BO57" s="32"/>
       <c r="BU57" s="4"/>
       <c r="BW57" s="4" t="s">
@@ -6471,7 +6495,9 @@
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
       <c r="L72" s="4"/>
-      <c r="N72" s="8"/>
+      <c r="N72" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="O72" s="9">
         <v>0</v>
       </c>
@@ -6524,7 +6550,9 @@
       <c r="BM72" s="10">
         <v>0</v>
       </c>
-      <c r="BN72" s="10"/>
+      <c r="BN72" s="10" t="s">
+        <v>126</v>
+      </c>
       <c r="BO72" s="32"/>
       <c r="BU72" s="4"/>
       <c r="CC72" s="3"/>
@@ -6542,7 +6570,9 @@
       <c r="E73" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N73" s="13"/>
+      <c r="N73" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="O73" s="14">
         <v>0</v>
       </c>
@@ -6589,7 +6619,9 @@
       <c r="BM73" s="15">
         <v>0</v>
       </c>
-      <c r="BN73" s="15"/>
+      <c r="BN73" s="15" t="s">
+        <v>107</v>
+      </c>
       <c r="BO73" s="32"/>
       <c r="BU73" s="4"/>
       <c r="BW73" s="4" t="s">

--- a/planilhas/Copa do Brasil.xlsx
+++ b/planilhas/Copa do Brasil.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kleberson\Desktop\meu-site - Copia\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2BE26B-C8ED-4987-9B8D-DC34DDE6C48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F8DD3E-96CA-4717-8031-4B7B6ACA8DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4F49A5ED-3A92-472E-8FA7-25B42F4FCE77}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4F49A5ED-3A92-472E-8FA7-25B42F4FCE77}"/>
   </bookViews>
   <sheets>
     <sheet name="Jogos" sheetId="1" r:id="rId1"/>
@@ -4470,7 +4470,7 @@
         <v>0</v>
       </c>
       <c r="BN40" s="10" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="BO40" s="32"/>
       <c r="BU40" s="4"/>

--- a/planilhas/Copa do Brasil.xlsx
+++ b/planilhas/Copa do Brasil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kleberson\Desktop\meu-site - Copia\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F8DD3E-96CA-4717-8031-4B7B6ACA8DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67FE78B-E5AD-4D44-9435-F42C24003671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4F49A5ED-3A92-472E-8FA7-25B42F4FCE77}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="155">
   <si>
     <t>IDA</t>
   </si>
@@ -461,6 +461,48 @@
   </si>
   <si>
     <t>FINAL JOGO ÚNICO</t>
+  </si>
+  <si>
+    <t>fazenda camaroes fc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cajá FCC           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Óia o rato!        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">mito350             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">expresso riachense  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM CBUM           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DINOO F.C 10        </t>
+  </si>
+  <si>
+    <t>Coquinho bebidas</t>
+  </si>
+  <si>
+    <t>TEAM CBUM</t>
+  </si>
+  <si>
+    <t>DINOO F.C 10</t>
+  </si>
+  <si>
+    <t>Cajá FCC</t>
+  </si>
+  <si>
+    <t>mito350</t>
+  </si>
+  <si>
+    <t>expresso riachense</t>
+  </si>
+  <si>
+    <t>Óia o rato!</t>
   </si>
 </sst>
 </file>
@@ -800,7 +842,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -961,6 +1003,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1418,8 +1466,8 @@
       <xdr:rowOff>122464</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>63</xdr:col>
-      <xdr:colOff>147840</xdr:colOff>
+      <xdr:col>62</xdr:col>
+      <xdr:colOff>447197</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>81642</xdr:rowOff>
     </xdr:to>
@@ -1895,7 +1943,7 @@
     <col min="16" max="16" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="4.28515625" style="3" customWidth="1"/>
-    <col min="20" max="20" width="25.42578125" style="3" customWidth="1"/>
+    <col min="20" max="20" width="30.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="5.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8.85546875" style="3" customWidth="1"/>
     <col min="23" max="23" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -1925,13 +1973,13 @@
     <col min="49" max="50" width="4.28515625" style="3" customWidth="1"/>
     <col min="51" max="51" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="5.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="5.42578125" style="3" customWidth="1"/>
     <col min="54" max="54" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="55" max="56" width="4.28515625" style="3" customWidth="1"/>
     <col min="57" max="57" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="8.85546875" style="3" customWidth="1"/>
     <col min="59" max="59" width="5.42578125" style="3" customWidth="1"/>
-    <col min="60" max="60" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="28.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="61" max="62" width="4.28515625" style="3" customWidth="1"/>
     <col min="63" max="63" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="64" max="64" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -2974,7 +3022,9 @@
       </c>
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
-      <c r="T24" s="8"/>
+      <c r="T24" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="U24" s="9">
         <v>0</v>
       </c>
@@ -3028,7 +3078,9 @@
       <c r="BG24" s="10">
         <v>0</v>
       </c>
-      <c r="BH24" s="10"/>
+      <c r="BH24" s="10" t="s">
+        <v>53</v>
+      </c>
       <c r="BI24" s="4"/>
       <c r="BJ24" s="4"/>
       <c r="BK24" s="12">
@@ -3089,7 +3141,9 @@
       </c>
       <c r="R25" s="16"/>
       <c r="S25" s="19"/>
-      <c r="T25" s="13"/>
+      <c r="T25" s="13" t="s">
+        <v>149</v>
+      </c>
       <c r="U25" s="14">
         <v>0</v>
       </c>
@@ -3143,7 +3197,9 @@
       <c r="BG25" s="15">
         <v>0</v>
       </c>
-      <c r="BH25" s="15"/>
+      <c r="BH25" s="15" t="s">
+        <v>151</v>
+      </c>
       <c r="BI25" s="16"/>
       <c r="BJ25" s="23"/>
       <c r="BK25" s="13">
@@ -4402,7 +4458,9 @@
       </c>
       <c r="R40" s="26"/>
       <c r="S40" s="28"/>
-      <c r="T40" s="8"/>
+      <c r="T40" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="U40" s="9">
         <v>0</v>
       </c>
@@ -4456,7 +4514,9 @@
       <c r="BG40" s="10">
         <v>0</v>
       </c>
-      <c r="BH40" s="10"/>
+      <c r="BH40" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="BI40" s="4"/>
       <c r="BJ40" s="4"/>
       <c r="BK40" s="12">
@@ -4504,7 +4564,9 @@
       </c>
       <c r="R41" s="4"/>
       <c r="S41" s="4"/>
-      <c r="T41" s="13"/>
+      <c r="T41" s="13" t="s">
+        <v>141</v>
+      </c>
       <c r="U41" s="14">
         <v>0</v>
       </c>
@@ -4558,7 +4620,9 @@
       <c r="BG41" s="15">
         <v>0</v>
       </c>
-      <c r="BH41" s="15"/>
+      <c r="BH41" s="15" t="s">
+        <v>152</v>
+      </c>
       <c r="BI41" s="16"/>
       <c r="BJ41" s="23"/>
       <c r="BK41" s="13">
@@ -5538,7 +5602,9 @@
       </c>
       <c r="R56" s="4"/>
       <c r="S56" s="4"/>
-      <c r="T56" s="8"/>
+      <c r="T56" s="8" t="s">
+        <v>88</v>
+      </c>
       <c r="U56" s="9">
         <v>0</v>
       </c>
@@ -5561,7 +5627,9 @@
       <c r="BG56" s="10">
         <v>0</v>
       </c>
-      <c r="BH56" s="10"/>
+      <c r="BH56" s="10" t="s">
+        <v>126</v>
+      </c>
       <c r="BK56" s="12">
         <f>BM56+BL56</f>
         <v>0</v>
@@ -5607,7 +5675,9 @@
       </c>
       <c r="R57" s="16"/>
       <c r="S57" s="19"/>
-      <c r="T57" s="13"/>
+      <c r="T57" s="13" t="s">
+        <v>148</v>
+      </c>
       <c r="U57" s="14">
         <v>0</v>
       </c>
@@ -5638,7 +5708,9 @@
       <c r="BG57" s="15">
         <v>0</v>
       </c>
-      <c r="BH57" s="15"/>
+      <c r="BH57" s="15" t="s">
+        <v>153</v>
+      </c>
       <c r="BI57" s="16"/>
       <c r="BJ57" s="23"/>
       <c r="BK57" s="13">
@@ -6510,7 +6582,9 @@
       </c>
       <c r="R72" s="26"/>
       <c r="S72" s="28"/>
-      <c r="T72" s="8"/>
+      <c r="T72" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="U72" s="9">
         <v>0</v>
       </c>
@@ -6539,7 +6613,9 @@
       <c r="BG72" s="10">
         <v>0</v>
       </c>
-      <c r="BH72" s="10"/>
+      <c r="BH72" s="10" t="s">
+        <v>124</v>
+      </c>
       <c r="BK72" s="12">
         <f>BM72+BL72</f>
         <v>0</v>
@@ -6585,7 +6661,9 @@
       </c>
       <c r="R73" s="4"/>
       <c r="S73" s="4"/>
-      <c r="T73" s="13"/>
+      <c r="T73" s="13" t="s">
+        <v>150</v>
+      </c>
       <c r="U73" s="14">
         <v>0</v>
       </c>
@@ -6606,7 +6684,9 @@
       <c r="BG73" s="15">
         <v>0</v>
       </c>
-      <c r="BH73" s="15"/>
+      <c r="BH73" s="15" t="s">
+        <v>154</v>
+      </c>
       <c r="BI73" s="16"/>
       <c r="BJ73" s="23"/>
       <c r="BK73" s="13">
@@ -7197,7 +7277,7 @@
     <col min="5" max="5" width="33.140625" style="34" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" style="34" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.140625" style="34" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.5703125" style="34" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.5703125" style="55" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27.85546875" style="34" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.140625" style="34"/>
     <col min="11" max="11" width="29.140625" style="34" bestFit="1" customWidth="1"/>
@@ -7225,7 +7305,7 @@
       </c>
       <c r="E2" s="35"/>
       <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="H2" s="56"/>
       <c r="M2" s="37"/>
     </row>
     <row r="3" spans="3:13" x14ac:dyDescent="0.25">
@@ -7236,7 +7316,9 @@
         <v>110</v>
       </c>
       <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
+      <c r="H3" s="56" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="4" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C4" s="34" t="s">
@@ -7247,7 +7329,9 @@
       </c>
       <c r="E4" s="35"/>
       <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
+      <c r="H4" s="56" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="5" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C5" s="34" t="s">
@@ -7258,7 +7342,9 @@
       </c>
       <c r="E5" s="35"/>
       <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
+      <c r="H5" s="56" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="6" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C6" s="34" t="s">
@@ -7269,7 +7355,9 @@
       </c>
       <c r="E6" s="35"/>
       <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
+      <c r="H6" s="56" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C7" s="34" t="s">
@@ -7280,7 +7368,9 @@
       </c>
       <c r="E7" s="35"/>
       <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
+      <c r="H7" s="56" t="s">
+        <v>141</v>
+      </c>
       <c r="M7" s="37"/>
     </row>
     <row r="8" spans="3:13" x14ac:dyDescent="0.25">
@@ -7292,7 +7382,9 @@
       </c>
       <c r="E8" s="35"/>
       <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
+      <c r="H8" s="56" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="9" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C9" s="34" t="s">
@@ -7303,7 +7395,9 @@
       </c>
       <c r="E9" s="35"/>
       <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
+      <c r="H9" s="56" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="10" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C10" s="34" t="s">
@@ -7314,7 +7408,9 @@
       </c>
       <c r="E10" s="35"/>
       <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
+      <c r="H10" s="56" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="11" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C11" s="34" t="s">
@@ -7325,7 +7421,7 @@
       </c>
       <c r="E11" s="35"/>
       <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
+      <c r="H11" s="56"/>
     </row>
     <row r="12" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C12" s="34" t="s">
@@ -7336,7 +7432,7 @@
       </c>
       <c r="E12" s="35"/>
       <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
+      <c r="H12" s="56"/>
     </row>
     <row r="13" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C13" s="34" t="s">
@@ -7347,7 +7443,7 @@
       </c>
       <c r="E13" s="35"/>
       <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
+      <c r="H13" s="56"/>
       <c r="I13" s="38"/>
     </row>
     <row r="14" spans="3:13" x14ac:dyDescent="0.25">
@@ -7359,7 +7455,7 @@
       </c>
       <c r="E14" s="35"/>
       <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
+      <c r="H14" s="56"/>
     </row>
     <row r="15" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C15" s="39" t="s">
@@ -7369,7 +7465,7 @@
         <v>25</v>
       </c>
       <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
+      <c r="H15" s="56"/>
     </row>
     <row r="16" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C16" s="39" t="s">
@@ -7380,7 +7476,7 @@
       </c>
       <c r="E16" s="35"/>
       <c r="G16" s="35"/>
-      <c r="H16" s="36"/>
+      <c r="H16" s="56"/>
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C17" s="34" t="s">
@@ -7391,7 +7487,7 @@
       </c>
       <c r="E17" s="36"/>
       <c r="G17" s="35"/>
-      <c r="H17" s="36"/>
+      <c r="H17" s="56"/>
     </row>
     <row r="18" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C18" s="39" t="s">
@@ -7402,7 +7498,7 @@
       </c>
       <c r="E18" s="36"/>
       <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
+      <c r="H18" s="56"/>
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C19" s="39" t="s">
@@ -7413,7 +7509,7 @@
       </c>
       <c r="E19" s="35"/>
       <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
+      <c r="H19" s="56"/>
     </row>
     <row r="20" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C20" s="39" t="s">
@@ -7424,7 +7520,7 @@
       </c>
       <c r="E20" s="35"/>
       <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
+      <c r="H20" s="56"/>
     </row>
     <row r="21" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C21" s="34" t="s">
@@ -7435,7 +7531,7 @@
       </c>
       <c r="E21" s="35"/>
       <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
+      <c r="H21" s="56"/>
     </row>
     <row r="22" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C22" s="34" t="s">
@@ -7446,7 +7542,7 @@
       </c>
       <c r="E22" s="35"/>
       <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
+      <c r="H22" s="56"/>
     </row>
     <row r="23" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C23" s="34" t="s">
@@ -7457,7 +7553,7 @@
       </c>
       <c r="E23" s="35"/>
       <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
+      <c r="H23" s="56"/>
     </row>
     <row r="24" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C24" s="39" t="s">
@@ -7468,7 +7564,7 @@
       </c>
       <c r="E24" s="35"/>
       <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
+      <c r="H24" s="56"/>
     </row>
     <row r="25" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C25" s="39" t="s">
@@ -7479,7 +7575,7 @@
       </c>
       <c r="E25" s="35"/>
       <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
+      <c r="H25" s="56"/>
     </row>
     <row r="26" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C26" s="34" t="s">
@@ -7490,7 +7586,7 @@
       </c>
       <c r="E26" s="35"/>
       <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
+      <c r="H26" s="56"/>
     </row>
     <row r="27" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C27" s="39" t="s">
@@ -7501,7 +7597,7 @@
       </c>
       <c r="E27" s="35"/>
       <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
+      <c r="H27" s="56"/>
     </row>
     <row r="28" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C28" s="34" t="s">
@@ -7511,7 +7607,7 @@
         <v>118</v>
       </c>
       <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
+      <c r="H28" s="56"/>
     </row>
     <row r="29" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C29" s="39" t="s">
@@ -7521,7 +7617,7 @@
         <v>99</v>
       </c>
       <c r="G29" s="35"/>
-      <c r="H29" s="36"/>
+      <c r="H29" s="56"/>
     </row>
     <row r="30" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C30" s="34" t="s">
@@ -7531,7 +7627,7 @@
         <v>120</v>
       </c>
       <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
+      <c r="H30" s="56"/>
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C31" s="34" t="s">
@@ -7541,7 +7637,7 @@
         <v>69</v>
       </c>
       <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
+      <c r="H31" s="56"/>
     </row>
     <row r="32" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C32" s="34" t="s">
@@ -7551,7 +7647,7 @@
         <v>19</v>
       </c>
       <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
+      <c r="H32" s="56"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C33" s="34" t="s">
@@ -7561,7 +7657,7 @@
         <v>26</v>
       </c>
       <c r="G33" s="35"/>
-      <c r="H33" s="35"/>
+      <c r="H33" s="56"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C34" s="34" t="s">
@@ -7896,8 +7992,8 @@
       <c r="C81" s="34"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C4:D90">
-    <sortCondition ref="D2:D90"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H3:H10">
+    <sortCondition ref="H3:H10"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/planilhas/Copa do Brasil.xlsx
+++ b/planilhas/Copa do Brasil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kleberson\Desktop\meu-site - Copia\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67FE78B-E5AD-4D44-9435-F42C24003671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41108E09-995A-4A4A-8217-4145453E5241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4F49A5ED-3A92-472E-8FA7-25B42F4FCE77}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="155">
   <si>
     <t>IDA</t>
   </si>
@@ -962,6 +962,12 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1003,12 +1009,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1423,7 +1423,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>99</xdr:col>
-      <xdr:colOff>479424</xdr:colOff>
+      <xdr:colOff>479425</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>231321</xdr:rowOff>
     </xdr:to>
@@ -1528,7 +1528,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>88</xdr:col>
-      <xdr:colOff>54429</xdr:colOff>
+      <xdr:colOff>54430</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>17160</xdr:rowOff>
     </xdr:to>
@@ -1948,7 +1948,7 @@
     <col min="22" max="22" width="8.85546875" style="3" customWidth="1"/>
     <col min="23" max="23" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="4.28515625" style="3" customWidth="1"/>
-    <col min="26" max="26" width="18.28515625" style="3" customWidth="1"/>
+    <col min="26" max="26" width="21.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="5.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -1974,7 +1974,7 @@
     <col min="51" max="51" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="5.42578125" style="3" customWidth="1"/>
-    <col min="54" max="54" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="24" style="3" bestFit="1" customWidth="1"/>
     <col min="55" max="56" width="4.28515625" style="3" customWidth="1"/>
     <col min="57" max="57" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="8.85546875" style="3" customWidth="1"/>
@@ -2244,89 +2244,89 @@
       <c r="CS14" s="1"/>
     </row>
     <row r="15" spans="2:97" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="H15" s="41" t="s">
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="H15" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="41"/>
-      <c r="N15" s="49" t="s">
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="N15" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="O15" s="50"/>
-      <c r="P15" s="50"/>
-      <c r="Q15" s="50"/>
-      <c r="T15" s="45" t="s">
+      <c r="O15" s="52"/>
+      <c r="P15" s="52"/>
+      <c r="Q15" s="52"/>
+      <c r="T15" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="U15" s="46"/>
-      <c r="V15" s="46"/>
-      <c r="W15" s="46"/>
-      <c r="Z15" s="47" t="s">
+      <c r="U15" s="48"/>
+      <c r="V15" s="48"/>
+      <c r="W15" s="48"/>
+      <c r="Z15" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="AA15" s="48"/>
-      <c r="AB15" s="48"/>
-      <c r="AC15" s="48"/>
-      <c r="AF15" s="53" t="s">
+      <c r="AA15" s="50"/>
+      <c r="AB15" s="50"/>
+      <c r="AC15" s="50"/>
+      <c r="AF15" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="AG15" s="54"/>
-      <c r="AH15" s="54"/>
-      <c r="AI15" s="54"/>
-      <c r="AL15" s="43" t="s">
+      <c r="AG15" s="56"/>
+      <c r="AH15" s="56"/>
+      <c r="AI15" s="56"/>
+      <c r="AL15" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="AM15" s="44"/>
-      <c r="AN15" s="44"/>
-      <c r="AO15" s="44"/>
-      <c r="AP15" s="44"/>
-      <c r="AS15" s="53" t="s">
+      <c r="AM15" s="46"/>
+      <c r="AN15" s="46"/>
+      <c r="AO15" s="46"/>
+      <c r="AP15" s="46"/>
+      <c r="AS15" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="AT15" s="54"/>
-      <c r="AU15" s="54"/>
-      <c r="AV15" s="54"/>
-      <c r="AY15" s="47" t="s">
+      <c r="AT15" s="56"/>
+      <c r="AU15" s="56"/>
+      <c r="AV15" s="56"/>
+      <c r="AY15" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="AZ15" s="48"/>
-      <c r="BA15" s="48"/>
-      <c r="BB15" s="48"/>
-      <c r="BE15" s="51" t="s">
+      <c r="AZ15" s="50"/>
+      <c r="BA15" s="50"/>
+      <c r="BB15" s="50"/>
+      <c r="BE15" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="BF15" s="52"/>
-      <c r="BG15" s="52"/>
-      <c r="BH15" s="52"/>
+      <c r="BF15" s="54"/>
+      <c r="BG15" s="54"/>
+      <c r="BH15" s="54"/>
       <c r="BI15" s="7"/>
       <c r="BJ15" s="7"/>
-      <c r="BK15" s="49" t="s">
+      <c r="BK15" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="BL15" s="50"/>
-      <c r="BM15" s="50"/>
-      <c r="BN15" s="50"/>
+      <c r="BL15" s="52"/>
+      <c r="BM15" s="52"/>
+      <c r="BN15" s="52"/>
       <c r="BO15" s="31"/>
-      <c r="BQ15" s="41" t="s">
+      <c r="BQ15" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="BR15" s="41"/>
-      <c r="BS15" s="41"/>
-      <c r="BT15" s="41"/>
+      <c r="BR15" s="43"/>
+      <c r="BS15" s="43"/>
+      <c r="BT15" s="43"/>
       <c r="BU15" s="31"/>
-      <c r="BW15" s="42" t="s">
+      <c r="BW15" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="BX15" s="42"/>
-      <c r="BY15" s="42"/>
-      <c r="BZ15" s="42"/>
+      <c r="BX15" s="44"/>
+      <c r="BY15" s="44"/>
+      <c r="BZ15" s="44"/>
       <c r="CC15" s="3"/>
       <c r="CD15" s="3"/>
       <c r="CE15" s="3"/>
@@ -2345,63 +2345,63 @@
       <c r="CS15" s="1"/>
     </row>
     <row r="16" spans="2:97" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="50"/>
-      <c r="P16" s="50"/>
-      <c r="Q16" s="50"/>
-      <c r="T16" s="46"/>
-      <c r="U16" s="46"/>
-      <c r="V16" s="46"/>
-      <c r="W16" s="46"/>
-      <c r="Z16" s="48"/>
-      <c r="AA16" s="48"/>
-      <c r="AB16" s="48"/>
-      <c r="AC16" s="48"/>
-      <c r="AF16" s="54"/>
-      <c r="AG16" s="54"/>
-      <c r="AH16" s="54"/>
-      <c r="AI16" s="54"/>
-      <c r="AL16" s="44"/>
-      <c r="AM16" s="44"/>
-      <c r="AN16" s="44"/>
-      <c r="AO16" s="44"/>
-      <c r="AP16" s="44"/>
-      <c r="AS16" s="54"/>
-      <c r="AT16" s="54"/>
-      <c r="AU16" s="54"/>
-      <c r="AV16" s="54"/>
-      <c r="AY16" s="48"/>
-      <c r="AZ16" s="48"/>
-      <c r="BA16" s="48"/>
-      <c r="BB16" s="48"/>
-      <c r="BE16" s="52"/>
-      <c r="BF16" s="52"/>
-      <c r="BG16" s="52"/>
-      <c r="BH16" s="52"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="52"/>
+      <c r="P16" s="52"/>
+      <c r="Q16" s="52"/>
+      <c r="T16" s="48"/>
+      <c r="U16" s="48"/>
+      <c r="V16" s="48"/>
+      <c r="W16" s="48"/>
+      <c r="Z16" s="50"/>
+      <c r="AA16" s="50"/>
+      <c r="AB16" s="50"/>
+      <c r="AC16" s="50"/>
+      <c r="AF16" s="56"/>
+      <c r="AG16" s="56"/>
+      <c r="AH16" s="56"/>
+      <c r="AI16" s="56"/>
+      <c r="AL16" s="46"/>
+      <c r="AM16" s="46"/>
+      <c r="AN16" s="46"/>
+      <c r="AO16" s="46"/>
+      <c r="AP16" s="46"/>
+      <c r="AS16" s="56"/>
+      <c r="AT16" s="56"/>
+      <c r="AU16" s="56"/>
+      <c r="AV16" s="56"/>
+      <c r="AY16" s="50"/>
+      <c r="AZ16" s="50"/>
+      <c r="BA16" s="50"/>
+      <c r="BB16" s="50"/>
+      <c r="BE16" s="54"/>
+      <c r="BF16" s="54"/>
+      <c r="BG16" s="54"/>
+      <c r="BH16" s="54"/>
       <c r="BI16" s="7"/>
       <c r="BJ16" s="7"/>
-      <c r="BK16" s="50"/>
-      <c r="BL16" s="50"/>
-      <c r="BM16" s="50"/>
-      <c r="BN16" s="50"/>
+      <c r="BK16" s="52"/>
+      <c r="BL16" s="52"/>
+      <c r="BM16" s="52"/>
+      <c r="BN16" s="52"/>
       <c r="BO16" s="31"/>
-      <c r="BQ16" s="41"/>
-      <c r="BR16" s="41"/>
-      <c r="BS16" s="41"/>
-      <c r="BT16" s="41"/>
+      <c r="BQ16" s="43"/>
+      <c r="BR16" s="43"/>
+      <c r="BS16" s="43"/>
+      <c r="BT16" s="43"/>
       <c r="BU16" s="31"/>
-      <c r="BW16" s="42"/>
-      <c r="BX16" s="42"/>
-      <c r="BY16" s="42"/>
-      <c r="BZ16" s="42"/>
+      <c r="BW16" s="44"/>
+      <c r="BX16" s="44"/>
+      <c r="BY16" s="44"/>
+      <c r="BZ16" s="44"/>
       <c r="CC16" s="3"/>
       <c r="CD16" s="3"/>
       <c r="CE16" s="3"/>
@@ -3803,7 +3803,9 @@
       <c r="S32" s="4"/>
       <c r="X32" s="4"/>
       <c r="Y32" s="24"/>
-      <c r="Z32" s="8"/>
+      <c r="Z32" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="AA32" s="9">
         <v>0</v>
       </c>
@@ -3845,7 +3847,9 @@
       <c r="BA32" s="10">
         <v>0</v>
       </c>
-      <c r="BB32" s="10"/>
+      <c r="BB32" s="10" t="s">
+        <v>151</v>
+      </c>
       <c r="BC32" s="32"/>
       <c r="BD32" s="4"/>
       <c r="BI32" s="4"/>
@@ -3871,7 +3875,9 @@
       <c r="S33" s="4"/>
       <c r="X33" s="4"/>
       <c r="Y33" s="24"/>
-      <c r="Z33" s="13"/>
+      <c r="Z33" s="13" t="s">
+        <v>69</v>
+      </c>
       <c r="AA33" s="14">
         <v>0</v>
       </c>
@@ -3913,7 +3919,9 @@
       <c r="BA33" s="15">
         <v>0</v>
       </c>
-      <c r="BB33" s="15"/>
+      <c r="BB33" s="15" t="s">
+        <v>57</v>
+      </c>
       <c r="BC33" s="32"/>
       <c r="BD33" s="4"/>
       <c r="BI33" s="4"/>
@@ -6143,7 +6151,9 @@
       <c r="S65" s="4"/>
       <c r="X65" s="4"/>
       <c r="Y65" s="24"/>
-      <c r="Z65" s="8"/>
+      <c r="Z65" s="8" t="s">
+        <v>148</v>
+      </c>
       <c r="AA65" s="9">
         <v>0</v>
       </c>
@@ -6168,7 +6178,9 @@
       <c r="BA65" s="10">
         <v>0</v>
       </c>
-      <c r="BB65" s="10"/>
+      <c r="BB65" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="BC65" s="32"/>
       <c r="BD65" s="4"/>
       <c r="BO65" s="4"/>
@@ -6206,7 +6218,9 @@
       <c r="S66" s="4"/>
       <c r="X66" s="4"/>
       <c r="Y66" s="24"/>
-      <c r="Z66" s="13"/>
+      <c r="Z66" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="AA66" s="14">
         <v>0</v>
       </c>
@@ -6227,7 +6241,9 @@
       <c r="BA66" s="15">
         <v>0</v>
       </c>
-      <c r="BB66" s="15"/>
+      <c r="BB66" s="15" t="s">
+        <v>154</v>
+      </c>
       <c r="BC66" s="32"/>
       <c r="BD66" s="4"/>
       <c r="BO66" s="4"/>
@@ -7277,7 +7293,7 @@
     <col min="5" max="5" width="33.140625" style="34" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" style="34" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.140625" style="34" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.5703125" style="55" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.5703125" style="41" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27.85546875" style="34" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.140625" style="34"/>
     <col min="11" max="11" width="29.140625" style="34" bestFit="1" customWidth="1"/>
@@ -7305,7 +7321,7 @@
       </c>
       <c r="E2" s="35"/>
       <c r="G2" s="35"/>
-      <c r="H2" s="56"/>
+      <c r="H2" s="42"/>
       <c r="M2" s="37"/>
     </row>
     <row r="3" spans="3:13" x14ac:dyDescent="0.25">
@@ -7316,7 +7332,7 @@
         <v>110</v>
       </c>
       <c r="G3" s="35"/>
-      <c r="H3" s="56" t="s">
+      <c r="H3" s="42" t="s">
         <v>142</v>
       </c>
     </row>
@@ -7329,7 +7345,7 @@
       </c>
       <c r="E4" s="35"/>
       <c r="G4" s="35"/>
-      <c r="H4" s="56" t="s">
+      <c r="H4" s="42" t="s">
         <v>148</v>
       </c>
     </row>
@@ -7342,7 +7358,7 @@
       </c>
       <c r="E5" s="35"/>
       <c r="G5" s="35"/>
-      <c r="H5" s="56" t="s">
+      <c r="H5" s="42" t="s">
         <v>147</v>
       </c>
     </row>
@@ -7355,7 +7371,7 @@
       </c>
       <c r="E6" s="35"/>
       <c r="G6" s="35"/>
-      <c r="H6" s="56" t="s">
+      <c r="H6" s="42" t="s">
         <v>145</v>
       </c>
     </row>
@@ -7368,7 +7384,7 @@
       </c>
       <c r="E7" s="35"/>
       <c r="G7" s="35"/>
-      <c r="H7" s="56" t="s">
+      <c r="H7" s="42" t="s">
         <v>141</v>
       </c>
       <c r="M7" s="37"/>
@@ -7382,7 +7398,7 @@
       </c>
       <c r="E8" s="35"/>
       <c r="G8" s="35"/>
-      <c r="H8" s="56" t="s">
+      <c r="H8" s="42" t="s">
         <v>144</v>
       </c>
     </row>
@@ -7395,7 +7411,7 @@
       </c>
       <c r="E9" s="35"/>
       <c r="G9" s="35"/>
-      <c r="H9" s="56" t="s">
+      <c r="H9" s="42" t="s">
         <v>143</v>
       </c>
     </row>
@@ -7408,7 +7424,7 @@
       </c>
       <c r="E10" s="35"/>
       <c r="G10" s="35"/>
-      <c r="H10" s="56" t="s">
+      <c r="H10" s="42" t="s">
         <v>146</v>
       </c>
     </row>
@@ -7421,7 +7437,7 @@
       </c>
       <c r="E11" s="35"/>
       <c r="G11" s="35"/>
-      <c r="H11" s="56"/>
+      <c r="H11" s="42"/>
     </row>
     <row r="12" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C12" s="34" t="s">
@@ -7432,7 +7448,7 @@
       </c>
       <c r="E12" s="35"/>
       <c r="G12" s="35"/>
-      <c r="H12" s="56"/>
+      <c r="H12" s="42"/>
     </row>
     <row r="13" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C13" s="34" t="s">
@@ -7443,7 +7459,7 @@
       </c>
       <c r="E13" s="35"/>
       <c r="G13" s="35"/>
-      <c r="H13" s="56"/>
+      <c r="H13" s="42"/>
       <c r="I13" s="38"/>
     </row>
     <row r="14" spans="3:13" x14ac:dyDescent="0.25">
@@ -7455,7 +7471,7 @@
       </c>
       <c r="E14" s="35"/>
       <c r="G14" s="35"/>
-      <c r="H14" s="56"/>
+      <c r="H14" s="42"/>
     </row>
     <row r="15" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C15" s="39" t="s">
@@ -7465,7 +7481,7 @@
         <v>25</v>
       </c>
       <c r="G15" s="35"/>
-      <c r="H15" s="56"/>
+      <c r="H15" s="42"/>
     </row>
     <row r="16" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C16" s="39" t="s">
@@ -7476,7 +7492,7 @@
       </c>
       <c r="E16" s="35"/>
       <c r="G16" s="35"/>
-      <c r="H16" s="56"/>
+      <c r="H16" s="42"/>
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C17" s="34" t="s">
@@ -7487,7 +7503,7 @@
       </c>
       <c r="E17" s="36"/>
       <c r="G17" s="35"/>
-      <c r="H17" s="56"/>
+      <c r="H17" s="42"/>
     </row>
     <row r="18" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C18" s="39" t="s">
@@ -7498,7 +7514,7 @@
       </c>
       <c r="E18" s="36"/>
       <c r="G18" s="35"/>
-      <c r="H18" s="56"/>
+      <c r="H18" s="42"/>
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C19" s="39" t="s">
@@ -7509,7 +7525,7 @@
       </c>
       <c r="E19" s="35"/>
       <c r="G19" s="35"/>
-      <c r="H19" s="56"/>
+      <c r="H19" s="42"/>
     </row>
     <row r="20" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C20" s="39" t="s">
@@ -7520,7 +7536,7 @@
       </c>
       <c r="E20" s="35"/>
       <c r="G20" s="35"/>
-      <c r="H20" s="56"/>
+      <c r="H20" s="42"/>
     </row>
     <row r="21" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C21" s="34" t="s">
@@ -7531,7 +7547,7 @@
       </c>
       <c r="E21" s="35"/>
       <c r="G21" s="35"/>
-      <c r="H21" s="56"/>
+      <c r="H21" s="42"/>
     </row>
     <row r="22" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C22" s="34" t="s">
@@ -7542,7 +7558,7 @@
       </c>
       <c r="E22" s="35"/>
       <c r="G22" s="35"/>
-      <c r="H22" s="56"/>
+      <c r="H22" s="42"/>
     </row>
     <row r="23" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C23" s="34" t="s">
@@ -7553,7 +7569,7 @@
       </c>
       <c r="E23" s="35"/>
       <c r="G23" s="35"/>
-      <c r="H23" s="56"/>
+      <c r="H23" s="42"/>
     </row>
     <row r="24" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C24" s="39" t="s">
@@ -7564,7 +7580,7 @@
       </c>
       <c r="E24" s="35"/>
       <c r="G24" s="35"/>
-      <c r="H24" s="56"/>
+      <c r="H24" s="42"/>
     </row>
     <row r="25" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C25" s="39" t="s">
@@ -7575,7 +7591,7 @@
       </c>
       <c r="E25" s="35"/>
       <c r="G25" s="35"/>
-      <c r="H25" s="56"/>
+      <c r="H25" s="42"/>
     </row>
     <row r="26" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C26" s="34" t="s">
@@ -7586,7 +7602,7 @@
       </c>
       <c r="E26" s="35"/>
       <c r="G26" s="35"/>
-      <c r="H26" s="56"/>
+      <c r="H26" s="42"/>
     </row>
     <row r="27" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C27" s="39" t="s">
@@ -7597,7 +7613,7 @@
       </c>
       <c r="E27" s="35"/>
       <c r="G27" s="35"/>
-      <c r="H27" s="56"/>
+      <c r="H27" s="42"/>
     </row>
     <row r="28" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C28" s="34" t="s">
@@ -7607,7 +7623,7 @@
         <v>118</v>
       </c>
       <c r="G28" s="35"/>
-      <c r="H28" s="56"/>
+      <c r="H28" s="42"/>
     </row>
     <row r="29" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C29" s="39" t="s">
@@ -7617,7 +7633,7 @@
         <v>99</v>
       </c>
       <c r="G29" s="35"/>
-      <c r="H29" s="56"/>
+      <c r="H29" s="42"/>
     </row>
     <row r="30" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C30" s="34" t="s">
@@ -7627,7 +7643,7 @@
         <v>120</v>
       </c>
       <c r="G30" s="35"/>
-      <c r="H30" s="56"/>
+      <c r="H30" s="42"/>
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C31" s="34" t="s">
@@ -7637,7 +7653,7 @@
         <v>69</v>
       </c>
       <c r="G31" s="35"/>
-      <c r="H31" s="56"/>
+      <c r="H31" s="42"/>
     </row>
     <row r="32" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C32" s="34" t="s">
@@ -7647,7 +7663,7 @@
         <v>19</v>
       </c>
       <c r="G32" s="35"/>
-      <c r="H32" s="56"/>
+      <c r="H32" s="42"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C33" s="34" t="s">
@@ -7657,7 +7673,7 @@
         <v>26</v>
       </c>
       <c r="G33" s="35"/>
-      <c r="H33" s="56"/>
+      <c r="H33" s="42"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C34" s="34" t="s">
